--- a/out/Рабочий файл 2025 MEBHOME (10) (1) (3) (1).xlsx
+++ b/out/Рабочий файл 2025 MEBHOME (10) (1) (3) (1).xlsx
@@ -41811,7 +41811,7 @@
         </is>
       </c>
       <c r="F365" s="78" t="n">
-        <v>27900</v>
+        <v>24900</v>
       </c>
       <c r="G365" s="76" t="inlineStr">
         <is>
